--- a/customer_service_forms/001_night_drop_envelope--customer_service_forms.xlsx
+++ b/customer_service_forms/001_night_drop_envelope--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>service_type</t>
+          <t>service_type_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Service Type</t>
+          <t>Service Type 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>customer_zip</t>
+          <t>customer_zip_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Customer Zip</t>
+          <t>Customer Zip 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>service_type</t>
+          <t>service_type_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Service Type</t>
+          <t>Service Type 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1301,19 +1301,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>service_type_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>service_type_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>service_type_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>service_type_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
